--- a/artfynd/A 13189-2023 artfynd.xlsx
+++ b/artfynd/A 13189-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13189-2023 artfynd.xlsx
+++ b/artfynd/A 13189-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90643482</v>
+        <v>91131420</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523963.9785194455</v>
+        <v>523903</v>
       </c>
       <c r="R2" t="n">
-        <v>7042930.942311965</v>
+        <v>7042892</v>
       </c>
       <c r="S2" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>91131422</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523901.0580249823</v>
+        <v>523901</v>
       </c>
       <c r="R3" t="n">
-        <v>7042856.809264177</v>
+        <v>7042857</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>96788658</v>
       </c>
       <c r="B4" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523901.8213968777</v>
+        <v>523902</v>
       </c>
       <c r="R4" t="n">
-        <v>7042874.225761089</v>
+        <v>7042874</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,19 +970,9 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1058,37 +1013,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91131420</v>
+        <v>90643482</v>
       </c>
       <c r="B5" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523903.0284092944</v>
+        <v>523964</v>
       </c>
       <c r="R5" t="n">
-        <v>7042892.091918747</v>
+        <v>7042931</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,19 +1081,9 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 13189-2023 artfynd.xlsx
+++ b/artfynd/A 13189-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96788658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,8 +1141,19 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90643482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>